--- a/资料/草稿.xlsx
+++ b/资料/草稿.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="64">
   <si>
     <t>共度时光</t>
   </si>
@@ -189,6 +189,36 @@
   </si>
   <si>
     <t>捉弄</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>通用奖励</t>
+  </si>
+  <si>
+    <t>可以送礼</t>
+  </si>
+  <si>
+    <t>可以邀约</t>
+  </si>
+  <si>
+    <t>可以学习1级技能</t>
+  </si>
+  <si>
+    <t>可以学习2级技能</t>
+  </si>
+  <si>
+    <t>可以学习3级技能</t>
+  </si>
+  <si>
+    <t>可以亲密互动</t>
+  </si>
+  <si>
+    <t>可以担任助手</t>
   </si>
 </sst>
 </file>
@@ -1361,7 +1391,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q40"/>
+  <dimension ref="A1:Q53"/>
   <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -1707,7 +1737,6 @@
       <c r="H20" t="s">
         <v>19</v>
       </c>
-      <c r="I20"/>
       <c r="K20" t="s">
         <v>18</v>
       </c>
@@ -1763,7 +1792,6 @@
       <c r="G27" t="s">
         <v>18</v>
       </c>
-      <c r="H27"/>
       <c r="K27" t="s">
         <v>19</v>
       </c>
@@ -1948,16 +1976,166 @@
         <v>19</v>
       </c>
     </row>
+    <row r="42" spans="2:3">
+      <c r="B42" t="s">
+        <v>54</v>
+      </c>
+      <c r="C42" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17">
+      <c r="B43">
+        <v>0</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17">
+      <c r="B44">
+        <v>10</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="P44">
+        <v>1</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17">
+      <c r="B45">
+        <v>20</v>
+      </c>
+      <c r="C45">
+        <v>2</v>
+      </c>
+      <c r="P45">
+        <v>2</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17">
+      <c r="B46">
+        <f>B44+B45</f>
+        <v>30</v>
+      </c>
+      <c r="C46">
+        <v>3</v>
+      </c>
+      <c r="P46">
+        <v>3</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17">
+      <c r="B47">
+        <f t="shared" ref="B47:B53" si="0">B45+B46</f>
+        <v>50</v>
+      </c>
+      <c r="C47">
+        <v>4</v>
+      </c>
+      <c r="P47">
+        <v>4</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17">
+      <c r="B48">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="C48">
+        <v>5</v>
+      </c>
+      <c r="P48">
+        <v>5</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="49" spans="2:17">
+      <c r="B49">
+        <f t="shared" si="0"/>
+        <v>130</v>
+      </c>
+      <c r="C49">
+        <v>6</v>
+      </c>
+      <c r="P49">
+        <v>6</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="50" spans="2:17">
+      <c r="B50">
+        <f t="shared" si="0"/>
+        <v>210</v>
+      </c>
+      <c r="C50">
+        <v>7</v>
+      </c>
+      <c r="P50">
+        <v>7</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="51" spans="2:16">
+      <c r="B51">
+        <f t="shared" si="0"/>
+        <v>340</v>
+      </c>
+      <c r="C51">
+        <v>8</v>
+      </c>
+      <c r="P51">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="2:16">
+      <c r="B52">
+        <f t="shared" si="0"/>
+        <v>550</v>
+      </c>
+      <c r="C52">
+        <v>9</v>
+      </c>
+      <c r="P52">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="2:16">
+      <c r="B53">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="C53">
+        <v>10</v>
+      </c>
+      <c r="P53">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="D$1:D$1048576">
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
-      <formula>"喜欢"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
-      <formula>"讨厌"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="$A1:$XFD1048576">
+  <conditionalFormatting sqref="Q46:Q48">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"喜欢"</formula>
     </cfRule>
@@ -1965,6 +2143,22 @@
       <formula>"讨厌"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E$1:XFD$1048576 D49:D1048576 A$1:C$1048576 D1:D45">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+      <formula>"讨厌"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+      <formula>"喜欢"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1:D45 D49:D1048576">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
+      <formula>"讨厌"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
+      <formula>"喜欢"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/资料/草稿.xlsx
+++ b/资料/草稿.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="11535"/>
   </bookViews>
   <sheets>
     <sheet name="草稿" sheetId="1" r:id="rId1"/>
@@ -27,17 +27,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="62">
   <si>
     <t>共度时光</t>
   </si>
   <si>
-    <t>每周每人只能共度一次时光</t>
-  </si>
-  <si>
-    <t>喜欢的子行为会标红心，厌恶的子行为会标心碎</t>
-  </si>
-  <si>
     <t>聊天</t>
   </si>
   <si>
@@ -77,7 +71,7 @@
     <t>光格尔</t>
   </si>
   <si>
-    <t>聊天话题会每周刷新</t>
+    <t>坦特里斯</t>
   </si>
   <si>
     <t>兴趣</t>
@@ -1394,594 +1388,613 @@
   <dimension ref="A1:Q53"/>
   <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="Q1" t="s">
+    </row>
+    <row r="4" spans="2:16">
+      <c r="B4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="17:17">
-      <c r="Q2" t="s">
+      <c r="D4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="2:17">
-      <c r="B4" t="s">
+      <c r="E4" t="s">
         <v>3</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>4</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
         <v>5</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
         <v>6</v>
       </c>
-      <c r="G4" t="s">
+      <c r="I4" t="s">
         <v>7</v>
       </c>
-      <c r="H4" t="s">
+      <c r="J4" t="s">
         <v>8</v>
       </c>
-      <c r="I4" t="s">
+      <c r="K4" t="s">
         <v>9</v>
       </c>
-      <c r="J4" t="s">
+      <c r="L4" t="s">
         <v>10</v>
       </c>
-      <c r="K4" t="s">
+      <c r="M4" t="s">
         <v>11</v>
       </c>
-      <c r="L4" t="s">
+      <c r="N4" t="s">
         <v>12</v>
       </c>
-      <c r="M4" t="s">
+      <c r="O4" t="s">
         <v>13</v>
       </c>
-      <c r="N4" t="s">
+      <c r="P4" t="s">
         <v>14</v>
-      </c>
-      <c r="O4" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="5" spans="3:10">
       <c r="C5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="3:16">
+      <c r="C6" t="s">
         <v>18</v>
       </c>
-      <c r="I5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="3:15">
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="O6" t="s">
-        <v>18</v>
+        <v>16</v>
+      </c>
+      <c r="P6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="3:13">
       <c r="C7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="3:15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="3:16">
       <c r="C8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O8" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="P8" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="3:13">
       <c r="C9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="3:14">
       <c r="C10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="3:11">
       <c r="C11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="3:8">
       <c r="C12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="3:13">
       <c r="C13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="3:13">
       <c r="C14" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I14" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K14" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L14" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M14" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="3:15">
       <c r="C15" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H15" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J15" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O15" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="3:14">
       <c r="C16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D16" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H16" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="3:12">
       <c r="C17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" t="s">
+        <v>16</v>
+      </c>
+      <c r="L17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16">
+      <c r="C18" t="s">
+        <v>30</v>
+      </c>
+      <c r="G18" t="s">
+        <v>16</v>
+      </c>
+      <c r="K18" t="s">
+        <v>16</v>
+      </c>
+      <c r="L18" t="s">
+        <v>16</v>
+      </c>
+      <c r="M18" t="s">
+        <v>16</v>
+      </c>
+      <c r="N18" t="s">
+        <v>16</v>
+      </c>
+      <c r="O18" t="s">
+        <v>17</v>
+      </c>
+      <c r="P18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16">
+      <c r="C19" t="s">
         <v>31</v>
       </c>
-      <c r="D17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F17" t="s">
-        <v>18</v>
-      </c>
-      <c r="L17" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="3:15">
-      <c r="C18" t="s">
+      <c r="D19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" t="s">
+        <v>17</v>
+      </c>
+      <c r="K19" t="s">
+        <v>17</v>
+      </c>
+      <c r="M19" t="s">
+        <v>17</v>
+      </c>
+      <c r="N19" t="s">
+        <v>16</v>
+      </c>
+      <c r="P19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="3:16">
+      <c r="C20" t="s">
         <v>32</v>
       </c>
-      <c r="G18" t="s">
-        <v>18</v>
-      </c>
-      <c r="K18" t="s">
-        <v>18</v>
-      </c>
-      <c r="L18" t="s">
-        <v>18</v>
-      </c>
-      <c r="M18" t="s">
-        <v>18</v>
-      </c>
-      <c r="N18" t="s">
-        <v>18</v>
-      </c>
-      <c r="O18" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="3:14">
-      <c r="C19" t="s">
-        <v>33</v>
-      </c>
-      <c r="D19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G19" t="s">
-        <v>19</v>
-      </c>
-      <c r="J19" t="s">
-        <v>19</v>
-      </c>
-      <c r="K19" t="s">
-        <v>19</v>
-      </c>
-      <c r="M19" t="s">
-        <v>19</v>
-      </c>
-      <c r="N19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="3:14">
-      <c r="C20" t="s">
-        <v>34</v>
-      </c>
       <c r="D20" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H20" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K20" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N20" t="s">
-        <v>18</v>
+        <v>16</v>
+      </c>
+      <c r="P20" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="2:17">
       <c r="B23" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="Q23" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="3:17">
       <c r="C24" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H24" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I24" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q24" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="3:15">
       <c r="C25" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O25" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="26" spans="3:8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16">
       <c r="C26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H26" t="s">
-        <v>18</v>
+        <v>16</v>
+      </c>
+      <c r="P26" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="27" spans="3:14">
       <c r="C27" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D27" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G27" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K27" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L27" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N27" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="3:8">
       <c r="C28" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H28" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="3:12">
       <c r="C29" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I29" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L29" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" spans="3:14">
       <c r="C30" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G30" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L30" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M30" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N30" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31" spans="3:11">
       <c r="C31" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D31" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J31" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K31" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" spans="3:10">
       <c r="C32" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="3:16">
+      <c r="C33" t="s">
+        <v>45</v>
+      </c>
+      <c r="L33" t="s">
+        <v>16</v>
+      </c>
+      <c r="O33" t="s">
+        <v>16</v>
+      </c>
+      <c r="P33" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="3:16">
+      <c r="C34" t="s">
         <v>46</v>
       </c>
-      <c r="D32" t="s">
-        <v>18</v>
-      </c>
-      <c r="G32" t="s">
-        <v>18</v>
-      </c>
-      <c r="H32" t="s">
-        <v>18</v>
-      </c>
-      <c r="J32" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="33" spans="3:15">
-      <c r="C33" t="s">
+      <c r="G34" t="s">
+        <v>16</v>
+      </c>
+      <c r="H34" t="s">
+        <v>16</v>
+      </c>
+      <c r="P34" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="3:16">
+      <c r="C35" t="s">
         <v>47</v>
       </c>
-      <c r="L33" t="s">
-        <v>18</v>
-      </c>
-      <c r="O33" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="34" spans="3:8">
-      <c r="C34" t="s">
-        <v>48</v>
-      </c>
-      <c r="G34" t="s">
-        <v>18</v>
-      </c>
-      <c r="H34" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="35" spans="3:14">
-      <c r="C35" t="s">
-        <v>49</v>
-      </c>
       <c r="D35" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G35" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H35" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I35" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L35" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N35" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="P35" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="37" spans="2:2">
       <c r="B37" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="38" spans="3:12">
       <c r="C38" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D38" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G38" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L38" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39" spans="3:15">
       <c r="C39" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D39" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G39" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O39" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40" spans="3:15">
       <c r="C40" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G40" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H40" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I40" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J40" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K40" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M40" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N40" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O40" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42" spans="2:3">
       <c r="B42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C42" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43" spans="2:17">
@@ -1992,7 +2005,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="44" spans="2:17">
@@ -2006,7 +2019,7 @@
         <v>1</v>
       </c>
       <c r="Q44" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="45" spans="2:17">
@@ -2020,7 +2033,7 @@
         <v>2</v>
       </c>
       <c r="Q45" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46" spans="2:17">
@@ -2035,7 +2048,7 @@
         <v>3</v>
       </c>
       <c r="Q46" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="47" spans="2:17">
@@ -2050,7 +2063,7 @@
         <v>4</v>
       </c>
       <c r="Q47" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="48" spans="2:17">
@@ -2065,7 +2078,7 @@
         <v>5</v>
       </c>
       <c r="Q48" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="49" spans="2:17">
@@ -2080,7 +2093,7 @@
         <v>6</v>
       </c>
       <c r="Q49" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="50" spans="2:17">
@@ -2095,7 +2108,7 @@
         <v>7</v>
       </c>
       <c r="Q50" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="51" spans="2:16">

--- a/资料/草稿.xlsx
+++ b/资料/草稿.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11535"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="草稿" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="62">
   <si>
     <t>共度时光</t>
   </si>
@@ -1543,7 +1543,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="3:14">
+    <row r="10" spans="3:16">
       <c r="C10" t="s">
         <v>22</v>
       </c>
@@ -1564,6 +1564,9 @@
       </c>
       <c r="N10" t="s">
         <v>16</v>
+      </c>
+      <c r="P10" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="3:11">

--- a/资料/草稿.xlsx
+++ b/资料/草稿.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="63">
   <si>
     <t>共度时光</t>
   </si>
@@ -72,6 +72,9 @@
   </si>
   <si>
     <t>坦特里斯</t>
+  </si>
+  <si>
+    <t>柯尔</t>
   </si>
   <si>
     <t>兴趣</t>
@@ -378,12 +381,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -704,7 +719,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -728,16 +743,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -746,90 +761,96 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1385,7 +1406,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q53"/>
+  <dimension ref="A1:S53"/>
   <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1393,653 +1414,656 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:16">
+    <row r="4" spans="2:17">
       <c r="B4" t="s">
         <v>1</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M4" t="s">
+      <c r="M4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N4" t="s">
+      <c r="N4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O4" t="s">
+      <c r="O4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="P4" t="s">
+      <c r="P4" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="3:10">
       <c r="C5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="3:16">
       <c r="C6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="3:13">
       <c r="C7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="3:16">
       <c r="C8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="3:13">
       <c r="C9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="3:16">
       <c r="C10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="3:11">
       <c r="C11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="3:8">
       <c r="C12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="3:13">
       <c r="C13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="3:13">
       <c r="C14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="3:15">
       <c r="C15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="3:14">
       <c r="C16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="3:12">
       <c r="C17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="3:16">
       <c r="C18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="3:16">
       <c r="C19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="3:16">
       <c r="C20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P20" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="2:17">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="2:19">
       <c r="B23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q23" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="24" spans="3:17">
+      <c r="S23" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19">
       <c r="C24" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H24" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I24" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>36</v>
+        <v>17</v>
+      </c>
+      <c r="S24" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="3:15">
       <c r="C25" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="3:16">
       <c r="C26" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H26" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P26" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="3:14">
       <c r="C27" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" spans="3:8">
       <c r="C28" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="3:12">
       <c r="C29" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" spans="3:14">
       <c r="C30" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" spans="3:11">
       <c r="C31" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D31" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J31" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K31" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32" spans="3:10">
       <c r="C32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33" spans="3:16">
       <c r="C33" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P33" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34" spans="3:16">
       <c r="C34" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G34" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H34" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P34" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="3:16">
       <c r="C35" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D35" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G35" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H35" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I35" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L35" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N35" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P35" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37" spans="2:2">
       <c r="B37" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="38" spans="3:12">
       <c r="C38" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D38" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G38" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L38" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="3:15">
       <c r="C39" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D39" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G39" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O39" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40" spans="3:15">
       <c r="C40" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G40" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H40" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I40" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J40" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K40" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M40" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N40" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O40" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42" spans="2:3">
       <c r="B42" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C42" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="43" spans="2:17">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19">
       <c r="B43">
         <v>0</v>
       </c>
       <c r="C43">
         <v>0</v>
       </c>
-      <c r="Q43" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="44" spans="2:17">
+      <c r="S43" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19">
       <c r="B44">
         <v>10</v>
       </c>
       <c r="C44">
         <v>1</v>
       </c>
-      <c r="P44">
+      <c r="R44">
         <v>1</v>
       </c>
-      <c r="Q44" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="45" spans="2:17">
+      <c r="S44" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19">
       <c r="B45">
         <v>20</v>
       </c>
       <c r="C45">
         <v>2</v>
       </c>
-      <c r="P45">
+      <c r="R45">
         <v>2</v>
       </c>
-      <c r="Q45" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="46" spans="2:17">
+      <c r="S45" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19">
       <c r="B46">
         <f>B44+B45</f>
         <v>30</v>
@@ -2047,14 +2071,14 @@
       <c r="C46">
         <v>3</v>
       </c>
-      <c r="P46">
+      <c r="R46">
         <v>3</v>
       </c>
-      <c r="Q46" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="47" spans="2:17">
+      <c r="S46" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19">
       <c r="B47">
         <f t="shared" ref="B47:B53" si="0">B45+B46</f>
         <v>50</v>
@@ -2062,14 +2086,14 @@
       <c r="C47">
         <v>4</v>
       </c>
-      <c r="P47">
+      <c r="R47">
         <v>4</v>
       </c>
-      <c r="Q47" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="48" spans="2:17">
+      <c r="S47" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19">
       <c r="B48">
         <f t="shared" si="0"/>
         <v>80</v>
@@ -2077,14 +2101,14 @@
       <c r="C48">
         <v>5</v>
       </c>
-      <c r="P48">
+      <c r="R48">
         <v>5</v>
       </c>
-      <c r="Q48" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="49" spans="2:17">
+      <c r="S48" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="49" spans="2:19">
       <c r="B49">
         <f t="shared" si="0"/>
         <v>130</v>
@@ -2092,14 +2116,14 @@
       <c r="C49">
         <v>6</v>
       </c>
-      <c r="P49">
+      <c r="R49">
         <v>6</v>
       </c>
-      <c r="Q49" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="50" spans="2:17">
+      <c r="S49" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="50" spans="2:19">
       <c r="B50">
         <f t="shared" si="0"/>
         <v>210</v>
@@ -2107,14 +2131,14 @@
       <c r="C50">
         <v>7</v>
       </c>
-      <c r="P50">
+      <c r="R50">
         <v>7</v>
       </c>
-      <c r="Q50" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="51" spans="2:16">
+      <c r="S50" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="51" spans="2:18">
       <c r="B51">
         <f t="shared" si="0"/>
         <v>340</v>
@@ -2122,11 +2146,11 @@
       <c r="C51">
         <v>8</v>
       </c>
-      <c r="P51">
+      <c r="R51">
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="2:16">
+    <row r="52" spans="2:18">
       <c r="B52">
         <f t="shared" si="0"/>
         <v>550</v>
@@ -2134,11 +2158,11 @@
       <c r="C52">
         <v>9</v>
       </c>
-      <c r="P52">
+      <c r="R52">
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="2:16">
+    <row r="53" spans="2:18">
       <c r="B53">
         <f t="shared" si="0"/>
         <v>890</v>
@@ -2146,12 +2170,52 @@
       <c r="C53">
         <v>10</v>
       </c>
-      <c r="P53">
+      <c r="R53">
         <v>10</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="Q46:Q48">
+  <conditionalFormatting sqref="F4">
+    <cfRule type="cellIs" dxfId="0" priority="12" operator="equal">
+      <formula>"喜欢"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="11" operator="equal">
+      <formula>"讨厌"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4">
+    <cfRule type="cellIs" dxfId="0" priority="10" operator="equal">
+      <formula>"喜欢"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="9" operator="equal">
+      <formula>"讨厌"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
+    <cfRule type="cellIs" dxfId="0" priority="8" operator="equal">
+      <formula>"喜欢"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="7" operator="equal">
+      <formula>"讨厌"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L4">
+    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
+      <formula>"喜欢"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
+      <formula>"讨厌"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M4">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+      <formula>"喜欢"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+      <formula>"讨厌"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N4">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"喜欢"</formula>
     </cfRule>
@@ -2159,19 +2223,27 @@
       <formula>"讨厌"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E$1:XFD$1048576 D49:D1048576 A$1:C$1048576 D1:D45">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+  <conditionalFormatting sqref="S46:S48">
+    <cfRule type="cellIs" dxfId="1" priority="13" operator="equal">
       <formula>"讨厌"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="14" operator="equal">
+      <formula>"喜欢"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U$1:XFD$1048576 S1:T53 P54:T1048576 D1:D45 D49:D1048576 Q1:R21 A$1:C$1048576 E$1:O$1048576 P1:P43 R22 R44:R53">
+    <cfRule type="cellIs" dxfId="1" priority="15" operator="equal">
+      <formula>"讨厌"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="16" operator="equal">
       <formula>"喜欢"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D45 D49:D1048576">
-    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="17" operator="equal">
       <formula>"讨厌"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="18" operator="equal">
       <formula>"喜欢"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/资料/草稿.xlsx
+++ b/资料/草稿.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="草稿" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="64">
   <si>
     <t>共度时光</t>
   </si>
@@ -186,6 +186,9 @@
   </si>
   <si>
     <t>捉弄</t>
+  </si>
+  <si>
+    <t>礼物</t>
   </si>
   <si>
     <t>Y</t>
@@ -1406,7 +1409,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S53"/>
+  <dimension ref="A1:S62"/>
   <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1461,7 +1464,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="3:10">
+    <row r="5" spans="3:17">
       <c r="C5" t="s">
         <v>16</v>
       </c>
@@ -1474,8 +1477,11 @@
       <c r="J5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" spans="3:16">
+      <c r="Q5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="3:17">
       <c r="C6" t="s">
         <v>19</v>
       </c>
@@ -1509,8 +1515,11 @@
       <c r="P6" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="7" spans="3:13">
+      <c r="Q6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="3:17">
       <c r="C7" t="s">
         <v>20</v>
       </c>
@@ -1532,8 +1541,11 @@
       <c r="M7" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="3:16">
+      <c r="Q7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="3:17">
       <c r="C8" t="s">
         <v>21</v>
       </c>
@@ -1549,8 +1561,11 @@
       <c r="P8" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="9" spans="3:13">
+      <c r="Q8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="3:17">
       <c r="C9" t="s">
         <v>22</v>
       </c>
@@ -1564,6 +1579,9 @@
         <v>17</v>
       </c>
       <c r="M9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q9" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1593,7 +1611,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="3:11">
+    <row r="11" spans="3:17">
       <c r="C11" t="s">
         <v>24</v>
       </c>
@@ -1603,8 +1621,11 @@
       <c r="K11" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="12" spans="3:8">
+      <c r="Q11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="3:17">
       <c r="C12" t="s">
         <v>25</v>
       </c>
@@ -1612,6 +1633,9 @@
         <v>17</v>
       </c>
       <c r="H12" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q12" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1629,7 +1653,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="3:13">
+    <row r="14" spans="3:17">
       <c r="C14" t="s">
         <v>27</v>
       </c>
@@ -1647,6 +1671,9 @@
       </c>
       <c r="M14" t="s">
         <v>17</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="3:15">
@@ -1666,7 +1693,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="3:14">
+    <row r="16" spans="3:17">
       <c r="C16" t="s">
         <v>29</v>
       </c>
@@ -1682,8 +1709,11 @@
       <c r="N16" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="17" spans="3:12">
+      <c r="Q16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="3:17">
       <c r="C17" t="s">
         <v>30</v>
       </c>
@@ -1698,6 +1728,9 @@
       </c>
       <c r="L17" t="s">
         <v>17</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="3:16">
@@ -1726,7 +1759,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="3:16">
+    <row r="19" spans="3:17">
       <c r="C19" t="s">
         <v>32</v>
       </c>
@@ -1751,8 +1784,11 @@
       <c r="P19" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="20" spans="3:16">
+      <c r="Q19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="3:17">
       <c r="C20" t="s">
         <v>33</v>
       </c>
@@ -1769,6 +1805,9 @@
         <v>17</v>
       </c>
       <c r="P20" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q20" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2016,161 +2055,166 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="2:3">
+    <row r="42" spans="2:2">
       <c r="B42" t="s">
         <v>53</v>
       </c>
-      <c r="C42" t="s">
+    </row>
+    <row r="51" spans="2:3">
+      <c r="B51" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="43" spans="2:19">
-      <c r="B43">
+      <c r="C51" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="52" spans="2:19">
+      <c r="B52">
         <v>0</v>
       </c>
-      <c r="C43">
+      <c r="C52">
         <v>0</v>
       </c>
-      <c r="S43" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="44" spans="2:19">
-      <c r="B44">
+      <c r="S52" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="53" spans="2:19">
+      <c r="B53">
         <v>10</v>
       </c>
-      <c r="C44">
+      <c r="C53">
         <v>1</v>
       </c>
-      <c r="R44">
+      <c r="R53">
         <v>1</v>
       </c>
-      <c r="S44" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="45" spans="2:19">
-      <c r="B45">
+      <c r="S53" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="54" spans="2:19">
+      <c r="B54">
         <v>20</v>
       </c>
-      <c r="C45">
+      <c r="C54">
         <v>2</v>
       </c>
-      <c r="R45">
+      <c r="R54">
         <v>2</v>
       </c>
-      <c r="S45" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="46" spans="2:19">
-      <c r="B46">
-        <f>B44+B45</f>
+      <c r="S54" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="55" spans="2:19">
+      <c r="B55">
+        <f>B53+B54</f>
         <v>30</v>
       </c>
-      <c r="C46">
+      <c r="C55">
         <v>3</v>
       </c>
-      <c r="R46">
+      <c r="R55">
         <v>3</v>
       </c>
-      <c r="S46" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="47" spans="2:19">
-      <c r="B47">
-        <f t="shared" ref="B47:B53" si="0">B45+B46</f>
+      <c r="S55" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="56" spans="2:19">
+      <c r="B56">
+        <f t="shared" ref="B56:B62" si="0">B54+B55</f>
         <v>50</v>
       </c>
-      <c r="C47">
+      <c r="C56">
         <v>4</v>
       </c>
-      <c r="R47">
+      <c r="R56">
         <v>4</v>
       </c>
-      <c r="S47" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="48" spans="2:19">
-      <c r="B48">
+      <c r="S56" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="57" spans="2:19">
+      <c r="B57">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="C48">
+      <c r="C57">
         <v>5</v>
       </c>
-      <c r="R48">
+      <c r="R57">
         <v>5</v>
       </c>
-      <c r="S48" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="49" spans="2:19">
-      <c r="B49">
+      <c r="S57" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="58" spans="2:19">
+      <c r="B58">
         <f t="shared" si="0"/>
         <v>130</v>
       </c>
-      <c r="C49">
+      <c r="C58">
         <v>6</v>
       </c>
-      <c r="R49">
+      <c r="R58">
         <v>6</v>
       </c>
-      <c r="S49" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="50" spans="2:19">
-      <c r="B50">
+      <c r="S58" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="59" spans="2:19">
+      <c r="B59">
         <f t="shared" si="0"/>
         <v>210</v>
       </c>
-      <c r="C50">
+      <c r="C59">
         <v>7</v>
       </c>
-      <c r="R50">
+      <c r="R59">
         <v>7</v>
       </c>
-      <c r="S50" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="51" spans="2:18">
-      <c r="B51">
+      <c r="S59" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="60" spans="2:18">
+      <c r="B60">
         <f t="shared" si="0"/>
         <v>340</v>
       </c>
-      <c r="C51">
+      <c r="C60">
         <v>8</v>
       </c>
-      <c r="R51">
+      <c r="R60">
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="2:18">
-      <c r="B52">
+    <row r="61" spans="2:18">
+      <c r="B61">
         <f t="shared" si="0"/>
         <v>550</v>
       </c>
-      <c r="C52">
+      <c r="C61">
         <v>9</v>
       </c>
-      <c r="R52">
+      <c r="R61">
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="2:18">
-      <c r="B53">
+    <row r="62" spans="2:18">
+      <c r="B62">
         <f t="shared" si="0"/>
         <v>890</v>
       </c>
-      <c r="C53">
+      <c r="C62">
         <v>10</v>
       </c>
-      <c r="R53">
+      <c r="R62">
         <v>10</v>
       </c>
     </row>
@@ -2223,7 +2267,7 @@
       <formula>"讨厌"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S46:S48">
+  <conditionalFormatting sqref="S55:S57">
     <cfRule type="cellIs" dxfId="1" priority="13" operator="equal">
       <formula>"讨厌"</formula>
     </cfRule>
@@ -2231,7 +2275,7 @@
       <formula>"喜欢"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U$1:XFD$1048576 S1:T53 P54:T1048576 D1:D45 D49:D1048576 Q1:R21 A$1:C$1048576 E$1:O$1048576 P1:P43 R22 R44:R53">
+  <conditionalFormatting sqref="S1:XFD40 R22 A1:P40 Q1:R21 R53:R62 U41:XFD1048576 P41:P52 S41:T62 E41:O1048576 A41:C1048576 P63:T1048576 D41:D54 D58:D1048576">
     <cfRule type="cellIs" dxfId="1" priority="15" operator="equal">
       <formula>"讨厌"</formula>
     </cfRule>
@@ -2239,7 +2283,7 @@
       <formula>"喜欢"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D45 D49:D1048576">
+  <conditionalFormatting sqref="D1:D54 D58:D1048576">
     <cfRule type="cellIs" dxfId="1" priority="17" operator="equal">
       <formula>"讨厌"</formula>
     </cfRule>
